--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1780,6 +1780,120 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>106567174</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56702</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578294</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6626727</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,7 +1785,7 @@
         <v>106567174</v>
       </c>
       <c r="B11" t="n">
-        <v>56702</v>
+        <v>56730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1893,6 +1893,374 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>106584958</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56726</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>578294</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6626727</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>106574285</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56693</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>578294</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6626727</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>106568841</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56701</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>578294</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6626727</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -1896,7 +1896,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106584958</v>
+        <v>106568219</v>
       </c>
       <c r="B12" t="n">
         <v>56726</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2K</t>
+          <t>2K+</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106574285</v>
+        <v>106568841</v>
       </c>
       <c r="B13" t="n">
-        <v>56693</v>
+        <v>56701</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100011</v>
+        <v>100001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2058,11 +2058,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>3K</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2107,7 +2103,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2113,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106568841</v>
+        <v>106574285</v>
       </c>
       <c r="B14" t="n">
-        <v>56701</v>
+        <v>56693</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,16 +2156,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100001</v>
+        <v>100011</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2182,7 +2178,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3K</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -1896,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106568219</v>
+        <v>106568841</v>
       </c>
       <c r="B12" t="n">
-        <v>56726</v>
+        <v>56701</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,16 +1912,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100067</v>
+        <v>100001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1934,11 +1934,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -2020,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106568841</v>
+        <v>106571559</v>
       </c>
       <c r="B13" t="n">
-        <v>56701</v>
+        <v>56726</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,16 +2032,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100001</v>
+        <v>100067</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2101,19 +2097,9 @@
           <t>2023-02-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1896,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106568841</v>
+        <v>106574285</v>
       </c>
       <c r="B12" t="n">
-        <v>56701</v>
+        <v>56693</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,16 +1912,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100001</v>
+        <v>100011</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1934,7 +1934,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3K</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1979,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1989,7 +1993,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106571559</v>
+        <v>106568841</v>
       </c>
       <c r="B13" t="n">
-        <v>56726</v>
+        <v>56701</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,16 +2036,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100067</v>
+        <v>100001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2097,9 +2101,19 @@
           <t>2023-02-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2126,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106574285</v>
+        <v>106571559</v>
       </c>
       <c r="B14" t="n">
-        <v>56693</v>
+        <v>56726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2142,16 +2156,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100011</v>
+        <v>100067</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2164,11 +2178,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>3K</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2211,19 +2221,9 @@
           <t>2023-02-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,6 +2247,126 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>106574288</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56829</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>578294</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6626727</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -1896,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106574285</v>
+        <v>106568219</v>
       </c>
       <c r="B12" t="n">
-        <v>56693</v>
+        <v>56726</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,16 +1912,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100011</v>
+        <v>100067</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>2K+</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106571559</v>
+        <v>106574285</v>
       </c>
       <c r="B14" t="n">
-        <v>56726</v>
+        <v>56693</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100067</v>
+        <v>100011</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2178,7 +2178,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3K</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2221,9 +2225,19 @@
           <t>2023-02-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -2020,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106568841</v>
+        <v>106574285</v>
       </c>
       <c r="B13" t="n">
-        <v>56701</v>
+        <v>56693</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100001</v>
+        <v>100011</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2058,7 +2058,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3K</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2113,7 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106574285</v>
+        <v>106568841</v>
       </c>
       <c r="B14" t="n">
-        <v>56693</v>
+        <v>56701</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2156,16 +2160,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100011</v>
+        <v>100001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2178,11 +2182,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>3K</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -1896,7 +1896,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106568219</v>
+        <v>106584958</v>
       </c>
       <c r="B12" t="n">
         <v>56726</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2K+</t>
+          <t>2K</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106574285</v>
+        <v>106568841</v>
       </c>
       <c r="B13" t="n">
-        <v>56693</v>
+        <v>56701</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100011</v>
+        <v>100001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2058,11 +2058,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>3K</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2107,7 +2103,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2113,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106568841</v>
+        <v>106574285</v>
       </c>
       <c r="B14" t="n">
-        <v>56701</v>
+        <v>56693</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,16 +2156,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100001</v>
+        <v>100011</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2182,7 +2178,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3K</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107557673</v>
+        <v>106574288</v>
       </c>
       <c r="B11" t="n">
-        <v>56311</v>
+        <v>57284</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,25 +1764,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100067</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1790,17 +1790,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1808,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578293.8011474541</v>
+        <v>578294</v>
       </c>
       <c r="R11" t="n">
-        <v>6626726.910248657</v>
+        <v>6626726</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1838,22 +1830,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,126 +1869,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>106574288</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>102977</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Picus viridis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>578294</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6626726</v>
-      </c>
-      <c r="S12" t="n">
-        <v>50</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Västerås</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Haraker</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Gustav Eriksson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Gustav Eriksson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7257214</v>
+        <v>106619168</v>
       </c>
       <c r="B2" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232272</v>
+        <v>1026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bastubacken, Svanå, Vstm</t>
+          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578136.8028780977</v>
+        <v>578294</v>
       </c>
       <c r="R2" t="n">
-        <v>6626993.643114124</v>
+        <v>6626726</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-04-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-04-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,74 +761,61 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>ML524</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Gustav Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Gustav Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106619168</v>
+        <v>106568841</v>
       </c>
       <c r="B3" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1026</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578293.8011474541</v>
+        <v>578294</v>
       </c>
       <c r="R3" t="n">
-        <v>6626726.910248657</v>
+        <v>6626726</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -888,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,12 +898,7 @@
         <v>106574285</v>
       </c>
       <c r="B4" t="n">
-        <v>57147</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,37 +1014,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106568841</v>
+        <v>107559595</v>
       </c>
       <c r="B5" t="n">
-        <v>57156</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1090,7 +1049,11 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1128,22 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,45 +1123,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106567184</v>
+        <v>106567807</v>
       </c>
       <c r="B6" t="n">
-        <v>57943</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1251,9 +1203,19 @@
           <t>2023-02-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,37 +1242,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106567181</v>
+        <v>106567174</v>
       </c>
       <c r="B7" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>102110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1320,7 +1277,11 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1390,32 +1351,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106567807</v>
+        <v>107557689</v>
       </c>
       <c r="B8" t="n">
-        <v>57181</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>102623</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1428,13 +1384,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1472,22 +1428,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,37 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106567174</v>
+        <v>106574288</v>
       </c>
       <c r="B9" t="n">
-        <v>57185</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102110</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1554,11 +1495,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1599,9 +1536,19 @@
           <t>2023-02-10</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,51 +1575,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107557701</v>
+        <v>106567181</v>
       </c>
       <c r="B10" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103037</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578293.8011474541</v>
+        <v>578294</v>
       </c>
       <c r="R10" t="n">
-        <v>6626726.910248657</v>
+        <v>6626726</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1710,22 +1648,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,32 +1680,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106574288</v>
+        <v>107557701</v>
       </c>
       <c r="B11" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>103037</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1787,12 +1710,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1830,22 +1757,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,6 +1786,227 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>106567184</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skalleåsen obspunkt 1, Harakers sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>578294</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6626726</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustav Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7257214</v>
+      </c>
+      <c r="B13" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bastubacken, Svanå, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>578137</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6626994</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2014-04-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2014-04-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>ML524</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61543-2023 artfynd.xlsx
+++ b/artfynd/A 61543-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106619168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106568841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106574285</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107559595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106567807</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106567174</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107557689</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106574288</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106567181</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1786,6 +1836,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107557701</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106567184</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,8 +2067,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7257214</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>